--- a/sum_daily_order/config/app_config.xlsx
+++ b/sum_daily_order/config/app_config.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -438,7 +438,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -597,7 +597,7 @@
           <t>日本_直邮店</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -633,7 +633,7 @@
           <t>越南_本土店</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -672,6 +672,86 @@
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>越南跨境目录名为 cross_border</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>本土店</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥_本土店</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>目录已预留；墨西哥日报脚本接入后再启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>直邮店</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥_直邮店</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>目录已预留；墨西哥日报脚本接入后再启用</t>
         </is>
       </c>
     </row>
@@ -725,7 +805,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>JP=日本，VN=越南。</t>
+          <t>JP=日本，VN=越南，MX=墨西哥。</t>
         </is>
       </c>
     </row>

--- a/sum_daily_order/config/app_config.xlsx
+++ b/sum_daily_order/config/app_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11540"/>
+    <workbookView windowWidth="28800" windowHeight="11480"/>
   </bookViews>
   <sheets>
     <sheet name="Stores" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
   <si>
     <t>enabled</t>
   </si>
@@ -72,22 +72,19 @@
     <t>1=启用，0=不运行</t>
   </si>
   <si>
-    <t>cross-border</t>
+    <t>cross_border</t>
   </si>
   <si>
     <t>跨境店</t>
   </si>
   <si>
-    <t>cross_border</t>
-  </si>
-  <si>
     <t>日本_跨境店</t>
   </si>
   <si>
     <t>日本跨境目录名为 cross-border</t>
   </si>
   <si>
-    <t>direct</t>
+    <t>direct_old</t>
   </si>
   <si>
     <t>直邮店</t>
@@ -96,6 +93,9 @@
     <t>日本_直邮店</t>
   </si>
   <si>
+    <t>direct_new</t>
+  </si>
+  <si>
     <t>VN</t>
   </si>
   <si>
@@ -120,13 +120,10 @@
     <t>墨西哥_本土店</t>
   </si>
   <si>
-    <t>目录已预留；墨西哥日报脚本接入后再启用</t>
-  </si>
-  <si>
-    <t>direct_old</t>
-  </si>
-  <si>
     <t>墨西哥_直邮店</t>
+  </si>
+  <si>
+    <t>直邮新店</t>
   </si>
   <si>
     <t>字段</t>
@@ -157,7 +154,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,13 +165,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -633,158 +623,161 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1132,14 +1125,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="7" width="18" customWidth="1"/>
+    <col min="1" max="1" width="10" style="3" customWidth="1"/>
+    <col min="2" max="3" width="14" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14" style="3" customWidth="1"/>
+    <col min="6" max="7" width="18" style="3" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1212,13 +1205,13 @@
         <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1232,16 +1225,16 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="H4" s="2"/>
     </row>
@@ -1250,22 +1243,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2"/>
     </row>
@@ -1280,45 +1273,43 @@
         <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1332,18 +1323,63 @@
         <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="3">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="F10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1365,7 +1401,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>7</v>
@@ -1376,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1384,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1392,7 +1428,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1400,7 +1436,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1408,7 +1444,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
